--- a/docs/import-template.xlsx
+++ b/docs/import-template.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -427,6 +427,8 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>วุฒิ(BACHELOR/MASTER/DOCTORATE)</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>หน่วยงาน</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ตำแหน่ง</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -500,6 +512,16 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>MASTER</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงยุติธรรม</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>นักทรัพยากรบุคคลชำนาญการพิเศษ</t>
         </is>
       </c>
     </row>
@@ -697,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -705,6 +727,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -733,6 +756,11 @@
           <t>ชื่อตำแหน่ง</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>หน่วยงาน</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -758,6 +786,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ชำนาญการพิเศษ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงยุติธรรม</t>
         </is>
       </c>
     </row>
